--- a/Final_Validity.xlsx
+++ b/Final_Validity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anthony\Desktop\peak_detector\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEB40A9A-8759-4DCF-846C-FF808E8386D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AAA556-D1C5-4772-BE76-86EABBCD15AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8DC5E736-AF77-4E0E-91F2-31C73D6083CB}"/>
   </bookViews>
